--- a/docs/reviews/2026-10-22-r03-radar-copy-workbook.xlsx
+++ b/docs/reviews/2026-10-22-r03-radar-copy-workbook.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet name="Hướng dẫn" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Câu theo contact" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Độ phủ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Đối chiếu hiện tại" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Câu deep_dive" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Độ phủ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Đối chiếu hiện tại" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Câu theo contact'!$A$1:$T$561</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Đối chiếu hiện tại'!$A$1:$K$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Đối chiếu hiện tại'!$A$1:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +51,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -82,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -103,6 +111,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -54554,6 +54566,6378 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I141"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="90" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>voice</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>sentence</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Số âm tiết</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Owner decision</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>Owner note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-sun</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Tách ra từng lớp, crush hay hăng say khoe chuyện đúng hôm bạn cạn năng lượng; nói thật tình trạng của mình rồi xem họ đáp thế nào, một lần chưa đủ để kết luận.</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-sun</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn kỹ hơn, có buổi bạn ấy mang tin mừng tới đúng lúc bạn cần được hỏi han, nên báo trước tình trạng của mình rồi xem hai đứa có chia lượt dễ hơn không.</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-sun</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Trong nếp sống chung, những tối người yêu hăng hái kể chuyện chỗ làm dễ trùng lúc bạn chỉ còn sức im lặng, nên thử hẹn giờ để kể rồi theo dõi vài tuần.</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-sun</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Đặt cạnh nhau, lúc người này nói liền mạch về mình dễ chồng lên lúc bạn đang cạn sức; rút ra sớm là quyền của bạn, và một buổi gặp chưa nói lên con người họ.</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>R03-true_node-square-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>true_node-square-sun</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Cách crush sống sôi nổi đôi khi làm bạn chao đảo với hướng mới đang tập, nên ghi lại lý do mình bắt đầu rồi xem sau vài lần gặp nó còn vững không.</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>R03-true_node-square-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>true_node-square-sun</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Đáng chú ý là lời rủ của bạn ấy hay rơi đúng lúc bạn đang giữ một nếp mới, nên kể bạn ấy nghe mình đang tập gì rồi xem lời rủ có đổi đi không.</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>R03-true_node-square-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>true_node-square-sun</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Mỗi lần bạn bàn chuyện đổi hướng, nếp quen của người yêu dễ thành lực kéo ngược; nói rõ từng bước nhỏ và đừng đọc phản ứng chậm của họ thành phản đối.</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>R03-true_node-square-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>true_node-square-sun</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Thứ hiện ra rõ nhất là giọng chắc nịch của người này đôi khi làm bạn lung lay; dùng lúc đó để hỏi lại hướng của mình, vì người khác không quyết thay bạn.</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-pluto-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-pluto</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ đi cùng là crush kể được những chuyện khó nói hơn khi bạn đáp bằng cái nhìn sáng sủa, miễn là bạn nghe trọn trước; xem lần sau họ có tự mở lời không.</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-pluto-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-pluto</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Theo lớp đọc này, sự vững tin của bạn dễ thành chỗ bám mỗi khi bạn ấy gặp chuyện khó; hỏi bạn ấy lúc này nên nghe hay nên góp ý, đừng tự đoán.</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-pluto-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-pluto</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Một mẫu hay lặp lại là người yêu nói ra nỗi lo sâu nhất vào những tối bạn giữ giọng bình tĩnh; ghi nhận trước khi động viên, rồi đối chiếu qua vài tuần.</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-pluto-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-pluto</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Trong đời thường, chuyện nghiêm túc với người này dễ thở hơn nhờ cách bạn nhìn rộng ra, nhưng hãy để họ nói hết, vì một lần dễ chịu chưa đủ để hiểu nhau.</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-sun</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Điểm gặp nhau ở đây là lời cổ vũ của bạn dễ làm crush kể nhiều hơn về điều họ theo đuổi; khen ở mức thật và xem sự hào hứng có đi hai chiều không.</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-sun</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Bạn thường nhận vai người cổ vũ sớm nhất mỗi lần bạn ấy cân nhắc một bước ngoặt; hỏi xem kiểu cổ vũ nào giúp được bạn ấy thật, thay vì đoán.</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-sun</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Đọc chậm lại, sự tin tưởng bạn đặt vào người yêu thường đi kèm những lần họ dám nhận việc lớn hơn; ăn mừng cả bước nhỏ, và nhớ đây chỉ là một lớp.</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>R03-jupiter-trine-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>jupiter-trine-sun</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Xu hướng ở đây là một lời ghi nhận cụ thể của bạn dễ khiến người này trình bày ý tưởng cởi mở hơn, nhưng cần vài lần thử mới biết nó có đều không.</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-square-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>mercury-square-sun</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn nằm ở thời điểm, vì lời góp ý của bạn hay đến ngay sau khi crush gửi một thành quả; đổi thứ tự thành ghi nhận trước, hỏi sau, rồi xem cuộc chat đổi ra sao.</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-square-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>mercury-square-sun</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Trong những buổi bàn kế hoạch, câu hỏi về rủi ro của bạn dễ đến sớm hơn lời ủng hộ, nên đảo thứ tự vài lần rồi đối chiếu với cách bạn ấy đáp.</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-square-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>mercury-square-sun</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Lớp này gợi rằng góp ý chi tiết của bạn dễ chen vào lúc người yêu đang kể một việc làm tốt; thử giữ lại một lúc và xem phản ứng có khác không.</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-square-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>mercury-square-sun</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Giữa bạn và người này, câu hỏi vặn đôi khi bật ra ngay lúc họ kể điều mình làm được; mở bằng một lời ghi nhận, rồi để ý không khí buổi trao đổi thay đổi ra sao.</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-trine-true_node-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>mercury-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Một điểm dễ thấy là ý tưởng bạn kể bâng quơ hay được crush hỏi thêm hoặc thử làm; nói như gợi ý mở, rồi để thời gian cho biết đó là nếp hay tình cờ.</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-trine-true_node-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>mercury-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn từ chiều của bạn, cách làm mới bạn gợi ý thường được bạn ấy mang về thử, còn câu nào thật sự giúp ích thì chỉ bạn ấy trả lời được, nên cứ hỏi.</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-trine-true_node-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>mercury-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Trong những bữa tối, câu hỏi bạn đặt ra dễ giúp người yêu vạch rõ bước tiếp theo; để họ tự trả lời, rồi xem hướng đó có thành hình qua vài tháng.</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-trine-true_node-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>mercury-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Đáng ghi nhận là ý kiến của bạn dễ thành gợi ý để người này ghi chép hoặc tìm hiểu thêm, còn họ dùng nó thế nào là chuyện của họ.</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>R03-saturn-trine-neptune-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>saturn-trine-neptune</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Đọc kỹ, sự thực tế của bạn dễ giúp giấc mơ còn mờ của crush có hình hài hơn; gợi ý một việc làm được ngay thay vì sửa cả kế hoạch, rồi xem họ có kể tiếp không.</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>R03-saturn-trine-neptune-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>saturn-trine-neptune</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Hình dung một buổi bạn ấy kể ý tưởng bay bổng còn bạn chia nó thành việc cụ thể, kiểu phối hợp này dễ chạy nếu hai bạn chốt trước ai lo phần nào, rồi xem sau một việc thật.</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>R03-saturn-trine-neptune-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>saturn-trine-neptune</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Theo nếp thường ngày, người yêu kể về một cuộc sống khác còn bạn dựng khung tiền và thời gian cho nó, nên để giấc mơ được nói trọn trước khi tính, rồi kiểm tra lại sau vài lần.</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>R03-saturn-trine-neptune-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>saturn-trine-neptune</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Ở chỗ làm, một câu hỏi rõ ràng của bạn dễ giúp ý tưởng còn mơ hồ của người này sáng ra, nhưng vài lần trao đổi thật mới cho biết nhịp này có đều không.</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-venus-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-venus</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Mẫu hay xuất hiện là lúc bạn bớt cố gây ấn tượng thì crush đáp lời nhẹ nhàng hơn; để ý điều đó qua nhiều lần, vì một buổi vui chưa nói lên nhiều.</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-venus-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-venus</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Thường thì mỗi lần bạn kể về điều mình mê, bạn ấy hưởng ứng bằng cách hỏi thêm hay rủ cùng làm; xem bạn có hưởng ứng lại theo cách tương tự không.</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-venus-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-venus</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn qua nhiều ngày, những hôm bạn tự tin làm việc mình giỏi thường đi cùng cử chỉ chăm sóc của người yêu; gọi tên cử chỉ đó, nhưng không cần phải giỏi mới được chăm.</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-venus-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-venus</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Giữa bạn và người này, một câu nói thật lòng thường nhận lại câu đáp cởi mở, vậy là đủ để bắt đầu, còn phần sâu hơn phải chờ thêm nhiều lần gặp.</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-jupiter-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-jupiter</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn nằm ở mức độ, bạn quan tâm vừa phải còn crush đáp bằng những đề nghị lớn, nên nói rõ nhịp bạn thấy thoải mái và nhìn việc họ làm qua vài tuần.</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-jupiter-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-jupiter</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Trong các buổi đi chơi, cách bạn tính từng khoản và cách bạn ấy chi rộng tay dễ lệch nhau; chốt cách chia trước khi đi, rồi xem vài lần sau việc này có nhẹ hơn không.</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-jupiter-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-jupiter</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Lớp này gợi một điểm dễ cấn về tiền, khi bạn quen dè dặt còn người yêu hay chi mạnh cho niềm vui chung; lập một khoản chung rồi xem lại sau một tháng.</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-jupiter-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-jupiter</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Điều cần đọc kỹ là những kế hoạch lớn người này đưa ra ngay lần đầu dễ làm bạn ngợp, nên nhìn vào những gì họ làm sau đó, và bạn được quyền đi chậm.</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-mars-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-mars</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Ở giai đoạn mới nhắn tin, một tin cụt lủn của crush dễ kéo tâm trạng bạn xuống cả buổi; nhớ rằng chữ trên màn hình thiếu rất nhiều ngữ cảnh, và hỏi thẳng vẫn rõ hơn đoán.</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-mars-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-mars</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Một điểm dễ cấn là bạn ấy chốt nhanh trong kế hoạch chung còn bạn cần thêm chút thời gian; nói ngay bằng một câu ngắn rồi xem lần sau bạn ấy có hỏi ý bạn không.</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-mars-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-mars</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Lúc người yêu làm việc nhà gấp gáp và nói gọn thường trùng lúc bạn đang nhạy cảm, nên hẹn trước một câu báo mình cần dừng, vì cách làm lành quan trọng hơn lần va chạm.</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-mars-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-mars</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Theo những gì lớp này cho thấy, lối nói thẳng và gấp của người này dễ để lại cảm giác khó chịu khá lâu; ghi nhận nó, và đừng vội gán ý xấu cho họ.</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mars-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mars</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Dấu hiệu thường gặp là những hôm bạn trầm hẳn, crush hay đề nghị một việc làm ngay như ghé mua đồ hay đi dạo một vòng; xem nhịp đó có giữ được khi họ cũng bận.</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mars-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mars</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Một nét riêng ở đây là bạn ấy giúp bằng hành động hơn là lời, như rủ đi bộ một vòng hay ghé qua nhà, nên báo lại cách nào đỡ bạn nhất.</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mars-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mars</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Ở nhà, sự chăm sóc của người yêu lúc bạn mệt thường hiện ra qua việc làm hơn là câu chữ; ghi lại vài lần như vậy rồi xem nó có còn đều khi cả hai cùng bận.</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mars-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mars</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Ở mức mới quen, người này đáp lời than của bạn bằng hành động, như gửi một mẹo hay đề nghị đỡ việc; nhận tới đâu là bạn chọn, vì một lần giúp chưa nói lên độ thân.</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mercury-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Thường xuất hiện ở đây là việc bạn nói ra điều đang rối dễ hơn sau vài tin nhắn qua lại với crush, nên ghi lại vài lần như thế trước khi dựa nhiều vào nó.</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mercury-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Trong tình bạn này, cách bạn ấy hỏi han dễ giúp bạn sắp những thứ đang rối thành lời; kể bao nhiêu là tùy bạn, và vài lần nữa sẽ cho biết đó có phải nếp quen.</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mercury-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Ở nhà, khoảng im lặng của bạn thường không kéo dài vì người yêu hay hỏi một câu rất bình thường mà trúng; ghi nhận điều đó, nhưng vẫn tự nói ra khi họ bận.</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-mercury-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Một tín hiệu nhỏ là sau vài phút trao đổi với người này, những việc đang rối trong đầu bạn dễ xếp lại gọn hơn; quan sát qua vài lần gặp trước khi kể nhiều chuyện riêng.</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mars-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mars</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Điều lớp này ghi nhận là sự ân cần nhỏ của bạn hay được crush trả lời bằng việc làm, như hẹn một buổi cụ thể; nhìn chuỗi hành động qua vài tuần thay vì một lời mời.</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mars-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mars</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Giữa hai bạn có một kiểu qua lại khá trơn, bạn chăm chút bằng lời và quà nhỏ còn bạn ấy đáp bằng việc như chở đi hay sửa đồ; hỏi nhau khi thấy lệch.</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mars-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mars</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhà, lời yêu thương của bạn thường được người yêu đáp bằng việc lên lịch hay lo việc chung, nên nói điều đó có ý nghĩa với bạn, rồi xem nhịp có đi cả hai chiều.</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mars-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mars</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Một quan sát đáng giữ là sự thân thiện của bạn dễ dẫn tới việc người này đề nghị làm chung một việc; bạn được quyền cân nhắc, vì một lời mời chưa nói lên mức thân.</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-sun</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Cụ thể hơn, một lời khen gọi đúng tên việc crush vừa làm được dễ làm cuộc chat ấm lên hơn lời khen chung; đọc phản hồi của họ qua vài lần, đừng qua một tin.</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-sun</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Vai quen của bạn là người ghi nhận khi bạn ấy vượt qua một việc khó, như sau kỳ thi hay buổi ra mắt sản phẩm, nên giữ thói quen nhắn một câu, rồi xem cách bạn ấy đáp.</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-sun</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Lớp đầu tiên là một câu cảm ơn có tên việc cụ thể, như “cảm ơn vì đã sửa vòi nước”, thường làm người yêu hăng hái hơn với việc chung; thử một tuần rồi xem nhà mình đổi gì.</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-sun</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn ở mức xã giao, một nhận xét thật về phần việc người này làm khéo thường mở ra cuộc nói chuyện dài hơn; giữ nó đúng mức bạn thấy, vì khen gượng dễ lộ.</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-sextile-moon-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>mars-sextile-moon</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Đáng chú ý là một lời rủ có giờ, có chỗ và dễ từ chối thường được crush trả lời nhanh hơn lời rủ chung chung, nên thử vài lần rồi mới rút ra điều gì.</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-sextile-moon-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>mars-sextile-moon</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Ở các kèo nhóm, bạn đứng ra lên lịch còn bạn ấy tới với tâm trạng thoải mái, một nhịp khá dễ đi; hỏi ý trước khi chốt, rồi xem bạn ấy có rủ lại không.</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-sextile-moon-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>mars-sextile-moon</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhịp sống chung, việc bạn tự lo một việc nhỏ mà không cần nhắc thường làm không khí êm hơn; sau một tuần, hỏi xem việc nào thật sự đỡ được họ.</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-sextile-moon-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>mars-sextile-moon</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Thứ dễ thấy là một câu bắt chuyện chậm rãi về điều đang diễn ra quanh hai người thường giúp người này nói nhiều hơn; vài lần trò chuyện nữa sẽ cho biết đó có là nhịp chung.</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-square-mercury-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>mars-square-mercury</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn nằm ở tốc độ, vì bạn thường đã chọn xong ngày giờ trong lúc crush vẫn đang hỏi từng điều nhỏ; chậm lại một nhịp, rồi xem qua vài kèo hai bên có đỡ lệch không.</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-square-mercury-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>mars-square-mercury</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Lúc bàn việc chung, bạn ấy thường giải thích nhiều bước trong lúc bạn đã sẵn sàng làm; nhắc lại ý chính của bạn ấy rồi mới phản biện, và xem không khí đổi ra sao.</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-square-mercury-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>mars-square-mercury</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Với chuyện chi tiêu chung, mỗi lần người yêu hỏi thêm cho rõ trước khi quyết, bạn dễ sốt ruột, nên trả lời từng câu một, rồi xem cuộc bàn có ngắn đi không.</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-square-mercury-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>mars-square-mercury</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Trong dự án chung, bạn thường bắt đầu làm trước khi người này nói xong các bước, và câu chữ dễ gắt lên; viết ra kế hoạch ngắn trước, vì vài lần phối hợp sẽ cho biết nhịp nào ổn.</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-trine-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>mars-trine-sun</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Một lớp dễ thấy là những buổi đi xem, đi chơi do bạn rủ thường là lúc crush cười nhiều và hào hứng nhất; gặp ngoài đời vài lần sẽ nói nhiều hơn mọi dòng tin nhắn.</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-trine-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>mars-trine-sun</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn qua những thử thách hai đứa từng làm, bạn hay là người rủ còn bạn ấy là người tỏa sáng khi làm, nên để bạn ấy tự nhận phần việc và hỏi lại khi thấy nhịp quá dày.</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-trine-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>mars-trine-sun</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn theo tuần, kế hoạch bạn khởi xướng như tập thể dục hay nấu món mới thường là chỗ người yêu thể hiện sở trường; luân phiên người khởi xướng, rồi sau một tháng hỏi nhau nhịp có vừa không.</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>R03-mars-trine-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>mars-trine-sun</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Trong công việc, ý tưởng bạn nêu ra thường được người này nhận lấy và làm tiếp phần của họ; giao trước một phần rõ ràng, vì ấn tượng đầu chưa nói lên cách phối hợp lâu dài.</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Điểm nổi bật là cách bạn diễn đạt về crush thường khiến họ kể thêm về chính mình, nên giữ phần hỏi nhiều hơn phần nhận xét, vì vài câu trúng ý chưa phải đã hiểu hết một người.</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Ở các buổi gặp nhóm, bạn hay là người gọi tên rõ nhất những việc bạn ấy làm giỏi; hỏi lại xem mô tả đó có đúng không, vì người được tả mới là người có tiếng nói cuối.</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Một lớp riêng là bạn hay đặt thành câu những điều người yêu còn nói lửng lơ về tương lai; nhắc lại cho họ nghe rồi hỏi có đúng không, vì tóm hộ khác quyết hộ.</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Lớp này cho thấy những lời bạn đáp người này thường đúng trọng tâm, nên buổi trao đổi đầu dễ trôi; để họ nói phần còn lại, vì trúng ý một lần chưa phải là hiểu nhau.</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-venus-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Nét đáng để ý là những tin nhắn bạn viết chăm chút thường được crush đáp lại nhanh và dài hơn; tận hưởng nhịp đó, nhưng chỉ vài tuần mới cho biết nó có bền không.</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-venus-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Đặt cạnh nhau, lời góp ý của bạn thường đến tai bạn ấy khá êm vì cách chọn chữ; thử nó ở một lần bất đồng thật, vì êm lúc bình thường chưa nói được lúc căng.</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-venus-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Theo nếp hằng ngày, những tin nhắn nhỏ kiểu “về cẩn thận nhé” của bạn thường được người yêu nhắc lại vào hôm sau, nên để ý xem chúng có thưa đi vào tuần bận không, rồi tự điều chỉnh.</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-conjunction-venus-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>mercury-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Một nét nhỏ là vài câu bạn hỏi về bài nhạc người này đang nghe đã đủ mở ra câu chuyện dài hơn; cứ đi chậm, vì dễ trò chuyện chưa phải là đã thân.</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-opposition-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>mercury-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ lệch ở đây là mỗi lần crush tự mô tả mình, bạn hay thấy ngay một góc ngược lại và nói luôn; giữ câu phản biện lại một nhịp, rồi xem cuộc chat nhẹ hơn hay căng hơn.</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-opposition-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>mercury-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhiều buổi cà phê, góc nhìn của bạn về một chuyện thường ngược với cách bạn ấy kể, nên xin phép trước khi phản biện, và để ý không khí giữa hai đứa sau mỗi lần bàn.</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H79" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-opposition-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>mercury-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Ở chuyện tính toán chung, bạn hay chỉ ra ngay chỗ chưa ổn trong một dự định người yêu vừa kể; hỏi thêm hai câu trước khi góp ý, rồi xem vài lần sau hai người có bớt căng không.</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>R03-mercury-opposition-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>mercury-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Ghi nhận đầu tiên là ý kiến của bạn và người này hay đứng ở hai đầu, kể cả trong chuyện nhỏ; để họ nói xong rồi mới đáp, vì khác góc nhìn không phải chuyện đúng sai.</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-opposition-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>moon-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Một lớp cần nói rõ là crush hay kể chuyện về mình rất sớm và rất nhiều, còn bạn mở lời chậm hơn hẳn, nên báo trước nhịp của mình, và nhớ khác tốc độ chưa phải dấu hiệu xấu.</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-opposition-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>moon-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Những tuần bạn ấy bận chạy dự án hay trùng lúc bạn mong một buổi ngồi gần nói chuyện; giữ một lịch cố định mỗi tháng rồi xem hai đứa có đỡ hụt nhau không.</t>
+        </is>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-opposition-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>moon-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Một mẫu dễ thấy là những mùa người yêu bận rộn bên ngoài, buổi tối của bạn ở nhà dài ra; đề xuất một tối cố định trong tuần, rồi xem một tháng sau có giữ được không.</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-opposition-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>moon-opposition-sun</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Trong một nhóm đông, người này thường đứng giữa câu chuyện còn bạn hay lùi ra rìa, nên chọn nói chuyện riêng vào dịp khác, vì một buổi tụ tập chưa đủ để nói gì về hai người.</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-sextile-mercury-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>moon-sextile-mercury</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Đáng để ý là một tin nhắn ngắn về ngày hôm nay của bạn thường mở ra cuộc trò chuyện thật hơn với crush; kể từng lớp nhỏ, và chỉ đi sâu khi thấy cuộc chat đi hai chiều.</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-sextile-mercury-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>moon-sextile-mercury</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Hay gặp ở hai bạn là một tin than thở ngắn của bạn được bạn ấy đáp bằng lời khá trúng; nhắn trước cũng được, miễn là nhìn xem bạn ấy có đang bận hay không.</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-sextile-mercury-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>moon-sextile-mercury</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Ở nhà, một câu báo ngắn kiểu “hôm nay mình hơi đuối” thường giúp người yêu chọn đúng cách đáp, nên thử vài tuần rồi xem hai bạn có bớt phải đoán nhau không.</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H88" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-sextile-mercury-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>moon-sextile-mercury</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Giữa bạn và người này, một lời than mệt bâng quơ dễ dẫn tới một cuộc trò chuyện thật hơn; kể vừa đủ với độ quen hiện tại, vì vài câu đồng cảm chưa đủ để biết nhau sâu.</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H89" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-moon-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-moon</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Một điểm dễ cấn là cách bạn và crush tìm lại sự yên lòng khác nhau, người kể ra, người lặng đi một lúc; hỏi thẳng kiểu nào dễ chịu hơn, và đừng tự viết nghĩa cho một khoảng lặng.</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-moon-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-moon</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Lúc một trong hai đứa xuống tinh thần, cách hai bạn tìm đến nhau dễ trật, người nhắn liên tục, người im một thời gian; thống nhất trước một câu báo “mình ổn, chỉ cần chút thời gian”.</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H91" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-moon-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-moon</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhà, những tối cả hai cùng mệt, người kể hết ra, người lại tìm góc riêng; mỗi người viết một việc nhỏ giúp mình dịu lại, rồi thử đổi lượt trong một tháng.</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H92" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-square-moon-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>moon-square-moon</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Trước cùng một chuyện buồn hay bực ở chỗ làm, người này và bạn thường phản ứng theo hai kiểu khác hẳn; chờ một nhịp rồi mới đáp, vì một lần lệch chưa đủ để hiểu ai.</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Lớp nổi rõ ở đây là bạn và crush hay bật cười cùng chỗ, chọn cùng món, nói cùng kiểu; điểm chung đó giúp làm quen, còn chỗ khác nhau sẽ lộ dần sau vài lần gặp.</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H94" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Thường gặp ở hai đứa là cả hai cùng xung phong dẫn nhóm, cùng có sẵn ý tưởng; chia rõ ai dẫn phần nào, rồi xem sau một việc chung cả hai có còn thoải mái không.</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Mục tiêu giống nhau giúp hai bạn dễ đi cùng hướng, nhưng ở buổi họp mặt cả hai dễ cùng giành phần kể; luân phiên người dẫn chuyện và hỏi lại nhau sau mỗi dịp lớn.</t>
+        </is>
+      </c>
+      <c r="G96" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H96" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-sun</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Một nét dễ nhận ra là người này nói chuyện, đùa và làm việc theo kiểu khá giống bạn, nên buổi đầu trôi nhanh; nghe thêm vài lần nữa, vì giống ở bề mặt chưa cho biết nhiều.</t>
+        </is>
+      </c>
+      <c r="G97" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H97" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-venus-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Điều hiện ra là những hôm bạn để lộ nét riêng của mình, crush thường đáp bằng câu hỏi và lời hẹn gặp lại; ghi lại qua vài tuần, vì vài lần trùng hợp chưa thành nếp.</t>
+        </is>
+      </c>
+      <c r="G98" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H98" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-venus-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C99" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn qua những lần gặp, bạn ấy hay nhớ những chi tiết nhỏ bạn từng kể và nhắc lại đúng lúc; ghi nhận điều đó, rồi xem bạn có làm điều tương tự cho bạn ấy không.</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H99" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-venus-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Một điều đáng ghi lại là người yêu hay chuẩn bị đúng những thứ nhỏ bạn quen dùng, như ly nước ấm, nên nói ra một lần như vậy mỗi tuần, đừng để nó thành mặc nhiên.</t>
+        </is>
+      </c>
+      <c r="G100" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H100" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-venus-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-venus</t>
+        </is>
+      </c>
+      <c r="C101" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Ở mức xã giao, người này thường cởi mở hơn vào những lúc bạn nói chuyện bằng giọng quen của mình; giữ sự tự nhiên đó, rồi để thời gian cho thấy phần còn lại.</t>
+        </is>
+      </c>
+      <c r="G101" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H101" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-square-mercury-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>sun-square-mercury</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn là ngay sau khi bạn khoe một thành quả, crush hay hỏi lại từng chi tiết nhỏ; trả lời trước rồi mới quyết có buồn không, và nhìn cả cuộc chat thay vì một câu.</t>
+        </is>
+      </c>
+      <c r="G102" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H102" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-square-mercury-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>sun-square-mercury</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Mỗi lần bạn kể dự định, câu hỏi dồn của bạn ấy dễ nghe như nghi ngờ, nên báo trước hôm nay bạn chỉ kể hay đang xin ý kiến, rồi xem cách đáp có đổi không.</t>
+        </is>
+      </c>
+      <c r="G103" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H103" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-square-mercury-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>sun-square-mercury</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Lời phân tích của người yêu đôi khi đến đúng lúc bạn chỉ định khoe; thử mở đầu bằng “chuyện này để khoe thôi”, rồi xem qua vài lần cách đáp có đổi không.</t>
+        </is>
+      </c>
+      <c r="G104" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H104" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-square-mercury-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>sun-square-mercury</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Lúc bạn đang trình bày, một câu hỏi thẳng của người này dễ nghe như thách thức; trả lời phần nội dung trước, vì một buổi họp chưa đủ để hiểu cách họ làm việc.</t>
+        </is>
+      </c>
+      <c r="G105" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H105" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-moon-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-moon</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="inlineStr">
+        <is>
+          <t>Một quan sát nhẹ là crush thường kể chuyện chậm rãi và dài hơn khi bạn giữ giọng bình thản; xem họ có tự tìm đến bạn để kể không, vì đó mới là tín hiệu rõ.</t>
+        </is>
+      </c>
+      <c r="G106" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H106" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-moon-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-moon</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="inlineStr">
+        <is>
+          <t>Nhìn lại những lần gần đây, bạn thường là chỗ bạn ấy ghé qua sau một ngày rối, và buổi gặp hay kết thúc nhẹ nhõm; vai này quý, nhưng cũng cần có ngày bạn được nghe lại.</t>
+        </is>
+      </c>
+      <c r="G107" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H107" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-moon-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-moon</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>Sau những ngày dài, người yêu thường tìm về các nếp nhỏ bạn giữ đều như bữa tối hay cuộc đi bộ; hỏi xem nếp nào nên giữ, vì lớp này không thấy hết đời sống hai người.</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-moon-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-moon</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>Một điều dễ thấy là sau một câu đùa nhẹ của bạn, người này thường nói nhiều và cười dễ hơn ở những buổi gặp chung; vui vì điều đó, nhưng đừng nhận phần giữ tâm trạng cho ai.</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-sun-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-sun</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>Xét theo những buổi đi chơi, năng lượng của bạn và crush thường lên xuống khá cùng nhịp; thử vài kiểu hoạt động khác nhau, và đừng coi một buổi vui là câu trả lời.</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-sun-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-sun</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>Lớp đọc này cho thấy hai đứa hay cùng hăng hái lúc khởi động một việc mới; để ý cả đoạn giữa, khi một người chững lại, vì đó mới là lúc biết hai bạn đỡ nhau ra sao.</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-sun-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-sun</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E112" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="inlineStr">
+        <is>
+          <t>Ở chuyện dài hạn, hai bạn thường bàn kế hoạch chung khá suôn và ít phải thuyết phục nhau; vẫn dành chỗ cho điều riêng từng người đang theo đuổi, vì cùng hướng không có nghĩa là giống hệt nhau.</t>
+        </is>
+      </c>
+      <c r="G112" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H112" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-trine-sun-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>sun-trine-sun</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F113" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhóm làm việc, nhịp nhận việc và tốc độ hoàn thành của bạn với người này khá giống nhau; giao nhau một phần nhỏ trước, vì một dự án suôn chưa nói lên cả chặng dài.</t>
+        </is>
+      </c>
+      <c r="G113" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mercury-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E114" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="inlineStr">
+        <is>
+          <t>Một nét dễ thấy là giọng nhắn tin ấm áp của bạn thường được crush tiếp lời dài hơn; giữ cách viết như bạn vẫn nói, rồi xem nhịp trả lời đó có đều qua vài tuần không.</t>
+        </is>
+      </c>
+      <c r="G114" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H114" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mercury-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>Thường gặp ở tình bạn này là sự quan tâm của bạn làm bạn ấy kể ra nhiều ý tưởng dở dang, nên hỏi tiếp một câu thay vì góp ý ngay, và xem bạn cũng được hỏi lại không.</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mercury-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>Những tối bạn hỏi han nhẹ nhàng thường là lúc người yêu nói ra điều còn vướng trong lòng; nghe hết rồi mới góp ý, và để ý những buổi như vậy có thưa đi lúc bận không.</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-trine-mercury-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>venus-trine-mercury</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>Đặt trong bối cảnh mới quen, một câu hỏi ân cần của bạn hay mở ra những ý kiến người này ít nói; ghi nhớ điều họ kể, vì vài buổi nói chuyện chưa vẽ ra cả một người.</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-moon-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-moon</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>Xét kỹ, bạn và crush thường chọn những buổi hẹn yên tĩnh và rời đi cùng lúc khi chỗ ồn lên; dễ chịu như vậy vẫn nên hỏi nhau bằng lời, vì đoán trúng nhiều lần vẫn có lần trật.</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-moon-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-moon</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="inlineStr">
+        <is>
+          <t>Trong những buổi ngồi không, hai đứa thường chọn cùng một cách thư giãn mà không cần bàn trước; cứ giữ những buổi đó, và thỉnh thoảng hỏi nhau một câu, vì quen nhịp nhau cũng có ngày lệch.</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-moon-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-moon</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="inlineStr">
+        <is>
+          <t>Đọc theo nếp nhà, giờ ngủ, giờ ăn và cách hai bạn nghỉ cuối tuần thường khớp mà ít phải bàn; viết lại vài điều mỗi người cần khi mệt, vì khớp lâu dễ làm hai bạn quên hỏi.</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-moon-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-moon</t>
+        </is>
+      </c>
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F121" s="9" t="inlineStr">
+        <is>
+          <t>Mới quen mà ngồi cạnh người này, những khoảng lặng thường trôi qua tự nhiên; gặp thêm vài lần trước khi kết luận điều gì, vì dễ chịu ban đầu chỉ là một lớp.</t>
+        </is>
+      </c>
+      <c r="G121" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-mars-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-mars</t>
+        </is>
+      </c>
+      <c r="C122" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn nằm ở nhịp tiến, vì một cử chỉ nhẹ của bạn có khi được crush đáp bằng những lời rủ dồn dập; báo nhịp của mình, rồi xem họ điều chỉnh thế nào qua vài lần.</t>
+        </is>
+      </c>
+      <c r="G122" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-mars-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-mars</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E123" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="inlineStr">
+        <is>
+          <t>Bạn chăm chút từng món quà, từng lời chúc, còn bạn ấy đáp lại gọn và thẳng; kể một lần mình hụt hẫng bằng giọng bình thường, rồi xem lần sau có khác không.</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H123" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-mars-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-mars</t>
+        </is>
+      </c>
+      <c r="C124" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E124" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="inlineStr">
+        <is>
+          <t>Ở những buổi tối chung, bạn mong một khoảng yên bên nhau còn người yêu lại rủ ra ngoài hay vận động, nên lên lịch xen kẽ hai kiểu tối, rồi xem sau vài tuần ai thấy thiếu điều gì.</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H124" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I124" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>R03-venus-square-mars-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>venus-square-mars</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="inlineStr">
+        <is>
+          <t>Lớp cần lưu ý là một câu chuyện phiếm thân thiện của bạn có lúc được người này đáp bằng lời mời gấp gáp; trả lời theo tốc độ của mình, vì một lần hiểu lệch chưa nói lên nhiều.</t>
+        </is>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H125" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-true_node-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E126" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="inlineStr">
+        <is>
+          <t>Sau những lời động viên ân cần của bạn, crush hay thử một điều mới như đi học một kỹ năng; cổ vũ nhưng để họ tự chọn, rồi xem họ có kể tiếp không.</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H126" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-true_node-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F127" s="9" t="inlineStr">
+        <is>
+          <t>Những lần bạn ấy đổi việc hay đổi hướng, bạn thường là người ở cạnh lo mấy việc nhỏ; đứng cạnh mà không quyết thay, và hỏi xem lúc nào nên lùi lại.</t>
+        </is>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H127" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-true_node-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E128" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="inlineStr">
+        <is>
+          <t>Lúc người yêu bắt đầu thử một hướng mới, những bữa cơm và lời hỏi han của bạn đi cùng các bước đầu; trò chuyện khi họ nhắc tới, vì đi cùng không có nghĩa là đi thay.</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H128" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I128" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>R03-moon-trine-true_node-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>moon-trine-true_node</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>Một điều nhỏ dễ thấy là khi bạn hỏi thăm trước, người này hay trình bày ý tưởng mới sớm hơn; góp ý vừa đủ khi được hỏi, vì sự cởi mở đó cần vài lần nữa mới rõ.</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H129" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>R03-neptune-trine-venus-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>neptune-trine-venus</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E130" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="inlineStr">
+        <is>
+          <t>Đáng để tâm là gu nghệ thuật bạn chia sẻ thường được crush đáp lại bằng một bài hát hay bức ảnh; tận hưởng, rồi đối chiếu với những gì họ làm khi gặp mặt.</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H130" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>R03-neptune-trine-venus-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>neptune-trine-venus</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F131" s="9" t="inlineStr">
+        <is>
+          <t>Thường thấy ở hai bạn là những ý tưởng viết, vẽ hay quay phim nảy ra rất nhanh khi ngồi cùng nhau; thử biến một ý thành việc làm thật, và xem ai thường là người khởi xướng.</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H131" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>R03-neptune-trine-venus-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>neptune-trine-venus</t>
+        </is>
+      </c>
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E132" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="inlineStr">
+        <is>
+          <t>Những bất ngờ nhỏ bạn bày ra như một tấm thiệp tự vẽ thường được người yêu nhắc lại nhiều lần; cân lại bằng chuyện tiền nhà, rồi xem cả hai nhịp có giữ được không.</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H132" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>R03-neptune-trine-venus-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>neptune-trine-venus</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F133" s="9" t="inlineStr">
+        <is>
+          <t>Một bộ phim hay một triển lãm có thể kéo bạn và người này vào cuộc nói chuyện rất dài; tận hưởng nó, rồi xem ngoài những chủ đề ấy hai người còn nói được gì với nhau.</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H133" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-true_node-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-true_node</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E134" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="inlineStr">
+        <is>
+          <t>Một điều lớp này ghi lại là vài nếp sống của bạn đôi khi được crush thử theo; vui với điều đó, và nhớ họ đi hướng nào vẫn là lựa chọn của họ.</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H134" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-true_node-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-true_node</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="inlineStr">
+        <is>
+          <t>Theo những lần gặp, bạn ấy hay mượn vài cách làm của bạn rồi biến tấu theo kiểu riêng; khen phần biến tấu đó, và để bạn ấy tự quyết đi tiếp tới đâu.</t>
+        </is>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="H135" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-true_node-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-true_node</t>
+        </is>
+      </c>
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E136" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="inlineStr">
+        <is>
+          <t>Trong nhà, nếp sinh hoạt của bạn như tập buổi sáng hay đọc trước khi ngủ dễ được người yêu thử theo; đừng biến nó thành cuộc so sánh, vì nhịp thay đổi của họ là của họ.</t>
+        </is>
+      </c>
+      <c r="G136" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H136" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-true_node-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-true_node</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>fit</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>Ở các buổi trao đổi công việc, người này hay hỏi lại cách bạn sắp xếp việc và thử áp dụng; chia sẻ như một cách làm chứ không phải cách đúng, vì hoàn cảnh mỗi người khác nhau.</t>
+        </is>
+      </c>
+      <c r="G137" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H137" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-uranus-crush-deep_dive</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-uranus</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="inlineStr">
+        <is>
+          <t>crush</t>
+        </is>
+      </c>
+      <c r="E138" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="inlineStr">
+        <is>
+          <t>Chỗ dễ cấn là crush hay đổi kèo khó đoán, vừa vui vừa làm lịch của bạn chông chênh; giữ vài việc cố định cho mình, rồi xem qua vài lần bạn thấy vui hay mệt.</t>
+        </is>
+      </c>
+      <c r="G138" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="H138" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-uranus-friend-deep_dive</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-uranus</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="inlineStr">
+        <is>
+          <t>Đi chơi với bạn ấy thường mở đầu bằng một kế hoạch và kết thúc ở một chỗ khác hẳn, nên nói trước điều bạn cần giữ nguyên, rồi xem sau vài chuyến bạn còn thấy hụt không.</t>
+        </is>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="H139" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-uranus-partner-deep_dive</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-uranus</t>
+        </is>
+      </c>
+      <c r="C140" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E140" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="inlineStr">
+        <is>
+          <t>Lớp này gợi rằng những đề xuất bất chợt của người yêu như dời nhà hay đổi việc dễ làm nếp quen của bạn chao đi; hẹn một buổi riêng để bàn chuyện lớn, rồi xem có đỡ hơn không.</t>
+        </is>
+      </c>
+      <c r="G140" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H140" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>R03-sun-conjunction-uranus-someone-deep_dive</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>sun-conjunction-uranus</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>friction</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="inlineStr">
+        <is>
+          <t>someone</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="inlineStr">
+        <is>
+          <t>deep_dive</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="inlineStr">
+        <is>
+          <t>Một điểm dễ cấn là lịch hẹn và hướng làm việc của người này hay đổi nhanh; nói rõ phần bạn nhận được tới đâu, vì sự mới lạ ban đầu chưa nói lên cách hợp tác lâu dài.</t>
+        </is>
+      </c>
+      <c r="G141" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="H141" s="9" t="inlineStr">
+        <is>
+          <t>Duyệt</t>
+        </is>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -77557,7 +83941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/reviews/2026-10-22-r03-radar-copy-workbook.xlsx
+++ b/docs/reviews/2026-10-22-r03-radar-copy-workbook.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Trạng thái</t>
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>BẢN NHÁP. Chưa nối vào code, chưa vào kho nền đã duyệt (fallback-approval). Không câu nào hiển thị cho người dùng cho tới khi owner duyệt và một PR riêng nối vào renderer.</t>
+          <t xml:space="preserve">Đã có quyết định theo uỷ quyền ngày 26/10/2026; Codex rà câu chữ, Claude review bản sửa. Chưa nối vào renderer hay kho fallback. Giọng thứ tư là deep_dive; 140 câu roast không dùng.</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>R03-moon-square-sun-partner-gentle_specific</t>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có những tối bạn cần được vỗ về đúng lúc người yêu hào hứng kể việc vừa làm xong; nói ra bạn cần gì sẽ nhẹ hơn. (Đoán ý người kia: “người yêu muốn được khen” gán nhu cầu bên trong như sự thật; thay bằng hành vi quan sát được (hào hứng kể). “thứ tự mong muốn” hơi cứng.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Có những tối bạn cần được vỗ về lúc người yêu hào hứng kể việc vừa xong; nói rõ bạn cần gì để cả hai cùng biết. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>R03-moon-square-sun-someone-gentle_specific</t>
@@ -2129,11 +2129,11 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Nếu bạn đang cần yên mà người này lại hào hứng kể nhiều chuyện, quá tải đến nhanh; nhận ra sớm giúp bạn chọn lúc dừng. (Bản cũ hơi phán xét (“kể chuyện mình không ngừng”)). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu bạn đang cần yên mà người này kể liền nhiều chuyện, bạn có thể thấy quá tải; nói rõ khi mình cần dừng. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>R03-moon-square-sun-someone-playful_grounded</t>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Người này hào hứng kể liền mấy chuyện, bạn thì đang muốn yên: chào tạm biệt lịch sự cũng là một kỹ năng. (Bản cũ chế giễu người kia (“phát trực tiếp chuyện đời họ”)). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Người này kể liền mấy chuyện, bạn thì muốn yên một chút: hôm nay xin phép tan ca nghe chuyện sớm. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-crush-playful_grounded</t>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn đang tập sống chậm, crush lại sống như phim hành động: kịch bản mới của bạn bị thử lửa hơi sớm. (Sai nghĩa: “bị thử vai” (thử vai = casting) không ra ý “bị thử thách”.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn đang tập sống chậm mà đã gật đầu theo crush đi khắp nơi: lịch mới thử được ba ngày, khoan nhận thêm kèo. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-friend-gentle_specific</t>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể cá tính rõ ràng của bạn ấy làm bạn lưỡng lự với hướng mình đang đi; kể bạn ấy nghe và hỏi bạn ấy hỗ trợ được gì. (“cái tôi rõ ràng” trong tiếng Việt thường mang nghĩa chê (ego), nghe như nhận xét xấu về bạn ấy; mục ma sát nên là “dễ cấn”, không phải “xấu”.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu lời rủ của bạn ấy làm bạn lưỡng lự với hướng đang đi, kể rõ điều bạn đang tập và hỏi bạn ấy có thể hỗ trợ gì. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-partner-straight_warm</t>
@@ -3185,11 +3185,11 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Khi bạn muốn đổi hướng sống, nếp sống người yêu đã quen có thể tạo ma sát; nói rõ thay đổi đó quan trọng với bạn ra sao. (Câu lủng củng: “cách người yêu đã quen là chính mình” không tự nhiên.). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Khi bạn muốn đổi hướng sống, nếp quen của người yêu có thể khiến hai người khó thống nhất; nói rõ thay đổi nào quan trọng với bạn. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-partner-gentle_specific</t>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể khi bạn kể về hướng mới, người yêu đáp lại dè dặt hơn bạn nghĩ; hỏi xem thay đổi đó chạm vào điều gì của hai người. (Đoán nội tâm: “chạm vào hình ảnh họ đang giữ” là suy đoán về người yêu, trừu tượng, không quan sát được; khung “hình ảnh … đang giữ” lặp lại.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Có thể khi bạn kể hướng mới, người yêu hỏi lại nhiều hơn bạn nghĩ; hỏi xem thay đổi nào hai người cần bàn thêm. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>R03-jupiter-trine-pluto-crush-playful_grounded</t>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Crush kể về nỗi sợ lớn nhất, bạn nghe hết rồi mới hỏi có muốn cùng nghĩ cách không: lạc quan đúng lúc, khá ổn. (Bản cũ khen đáp nỗi sợ bằng kế hoạch, trái các câu “nghe trước”). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Crush kể nỗi sợ, bạn nghe hết rồi mới hỏi có muốn cùng nghĩ cách không: đội cứu hộ hôm nay nhớ xin phép trước. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>R03-jupiter-trine-sun-friend-straight_warm</t>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Khi bạn ấy đứng trước quyết định lớn, bạn thường là người lên tiếng tin bạn ấy đầu tiên; nói điều đó thật rõ, đừng để bạn ấy phải đoán. (Đoán nội tâm: “tin vào bạn ấy nhiều hơn chính bạn ấy” khẳng định bạn ấy thiếu tự tin như sự thật.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Khi bạn ấy đứng trước quyết định lớn, một lời động viên cụ thể của bạn có thể giúp ích; hỏi bạn ấy muốn nghe hay cần góp ý. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>R03-jupiter-trine-sun-friend-playful_grounded</t>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn ấy nói muốn đi hát, bạn đã đặt luôn sân khấu: quản lý tài năng tự phong. (“bẩm sinh” gợi tính cách định sẵn từ khi sinh, gần định mệnh trong bối cảnh lá số; “tự phong” giữ chất đùa.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn ấy vừa nhắc chuyện đi hát, bạn đã xung phong đặt phòng: quản lý tự phong nhớ hỏi ca sĩ trước. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-square-sun-crush-gentle_specific</t>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Một câu góp ý nhỏ khi nhắn tin có thể rơi đúng vào điều crush vừa hào hứng khoe; chậm lại một nhịp khi chọn chữ. (Đoán ý người kia: “điều crush đang muốn được công nhận” gán nhu cầu bên trong; thay bằng hành vi thấy được (vừa khoe).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Một câu góp ý khi nhắn tin có thể đến ngay lúc crush vừa khoe thành quả; ghi nhận việc ấy trước khi hỏi thêm. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-square-sun-partner-gentle_specific</t>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="T75" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Những lời nhận xét bạn thấy rất bình thường có thể rơi đúng lúc người yêu đang khoe việc vừa làm được; để ý phản ứng ngay sau câu đó. (Đoán ý người kia: “chỗ người yêu đang muốn được tự hào” gán nhu cầu bên trong, câu cũng hơi tối nghĩa.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Lời nhận xét bạn thấy bình thường có thể đến lúc người yêu vừa khoe việc làm được; để ý phản ứng rồi hỏi lại nếu chưa rõ. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-square-sun-someone-gentle_specific</t>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="T79" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể câu hỏi thẳng của bạn đến đúng lúc người này đang kể điều họ làm tốt; một câu ghi nhận trước giúp câu hỏi được nghe đúng ý. (Đoán nội tâm: “hình ảnh người này đang giữ” không quan sát được; khung “hình ảnh … đang giữ” lặp với true_node-square-sun-partner.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu câu hỏi thẳng của bạn đến lúc người này kể việc làm tốt, ghi nhận phần cụ thể trước rồi mới hỏi thêm. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-trine-true_node-someone-gentle_specific</t>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="T95" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Nếu bạn để ý, có thể sau vài câu bạn nói người này hỏi thêm về một hướng mới; cứ chia sẻ, không cần biết trước kết quả. (Không quan sát được: “khiến người này nghĩ về một hướng mới” nói về suy nghĩ người kia; đổi sang hành vi (hỏi thêm).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu sau vài câu bạn nói, người này hỏi thêm về một hướng mới, cứ chia sẻ điều mình biết và để họ tự chọn. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="60" customHeight="1">
       <c r="A128" s="4" t="inlineStr">
         <is>
           <t>R03-sun-trine-venus-someone-playful_grounded</t>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="T128" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn nói thật lòng một câu, người này cũng đáp lại cởi mở hơn: kết nối không cần kịch bản, chỉ cần bớt chỉnh filter. (Khẳng định cảm xúc người kia không rào: “đáp lại bằng thiện cảm”; đổi sang hành vi thấy được.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn bỏ bản nháp thứ năm, gửi một câu thật lòng, người này cũng kể thêm: cuộc chat hôm nay bớt một biên tập viên. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="60" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
           <t>R03-venus-square-jupiter-crush-straight_warm</t>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="T130" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Khi bạn thể hiện quan tâm vừa phải, crush có thể đáp lại bằng những dự định lớn; hỏi thử một bước cụ thể hai bạn làm được trong tuần này. (Bản cũ ngầm cảnh báo crush không đáng tin). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Khi bạn quan tâm vừa phải, crush có thể nhắc những dự định lớn; hỏi một bước cụ thể hai bạn làm được tuần này. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
         </is>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="60" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
         <is>
           <t>R03-moon-square-mars-partner-playful_grounded</t>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="T156" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Người yêu xắn tay dọn nhà như đánh trận, bạn thì đang cần một cái ôm: chỉ lệch giờ thôi, hẹn lại ca ôm sau khi dọn xong. (Phán xét ngầm: “sai giờ chứ không sai người” ngụ ý “đúng người” (verdict/định mệnh).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Người yêu đang dọn nhà, bạn lại đứng chờ ôm: gửi yêu cầu đúng lúc máy hút bụi nghỉ giải lao nhé. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -16341,7 +16341,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="60" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
         <is>
           <t>R03-moon-trine-mars-crush-playful_grounded</t>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="T164" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn đăng story mưa buồn, crush nhắn rủ đi ăn lẩu: phản xạ khá nhanh nhạy, để ý thêm vài lần nữa rồi tính. (Ẩn dụ chấm điểm: “chấm thêm vài lần” là chấm điểm người kia, đi ngược quy tắc không điểm.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn đăng story mưa buồn, crush rủ ăn lẩu: lòng đã ấm chưa thì chưa biết, nồi lẩu trước mắt có vẻ được. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -17109,7 +17109,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="60" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
         <is>
           <t>R03-moon-trine-mars-partner-playful_grounded</t>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="T172" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn thở dài một tiếng, người yêu đã dắt xe đi mua cháo: nhanh hơn cả app giao đồ, nhớ cảm ơn bằng lời. (Ẩn dụ chấm điểm: “đánh giá năm sao”; khung “hệ thống …” lặp 4 lần trong playful_grounded.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn thở dài, người yêu hỏi có cần mua cháo không: chưa kịp mở app giao đồ, nhớ nói mình cần gì nhé. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
         </is>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="48" customHeight="1">
       <c r="A211" s="4" t="inlineStr">
         <is>
           <t>R03-venus-trine-sun-crush-gentle_specific</t>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="T211" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể cách bạn quan tâm sẽ chạm đúng điều crush hay kể về mình; để ý phản hồi thật của họ sau lời khen. (Đoán ý người kia: “chỗ crush muốn được nhìn thấy” gán nhu cầu bên trong.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Có thể lời khen về điều crush hay kể làm cuộc chat cởi mở hơn; để ý cách họ đáp qua vài lần. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -22101,7 +22101,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="60" customHeight="1">
       <c r="A224" s="4" t="inlineStr">
         <is>
           <t>R03-venus-trine-sun-someone-playful_grounded</t>
@@ -22193,7 +22193,7 @@
       </c>
       <c r="T224" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Một lời khen đúng chỗ của bạn làm buổi làm quen bớt gượng hẳn: chất xúc tác giao tiếp, không có tác dụng phụ. (“dầu bôi trơn” dễ gợi nghĩa tình dục trong tiếng Việt; lệch ngữ cảnh someone (đồng nghiệp, mới quen).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn khen đúng chi tiết người này vừa kể, cuộc nói chuyện bớt gượng: lời khen không cần chạy thử mười bản. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
         </is>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="48" customHeight="1">
       <c r="A243" s="4" t="inlineStr">
         <is>
           <t>R03-mars-square-mercury-crush-gentle_specific</t>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="T243" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể sự nôn nóng của bạn gặp lúc crush còn đang hỏi kỹ để cân nhắc; để họ nói hết rồi hãy đề nghị tiếp. (Câu lủng củng: “chạm vào cách crush cần cân nhắc bằng lời” khó hiểu và gán nhu cầu.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu bạn muốn chốt nhanh lúc crush còn hỏi kỹ, để họ nói hết rồi mới đề nghị bước tiếp theo. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -29013,7 +29013,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="48" customHeight="1">
       <c r="A296" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-conjunction-venus-friend-playful_grounded</t>
@@ -29105,7 +29105,7 @@
       </c>
       <c r="T296" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Hai đứa có thể nói về một quán bánh suốt hai tiếng: chưa ăn mà đã no vì bàn tán. (Lặp khung: “hội … không lương” (cả hai khung lặp cùng lúc).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Hai đứa bàn về quán bánh suốt hai tiếng: chưa ăn miếng nào mà thực đơn đã thuộc lòng. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -30453,7 +30453,7 @@
         </is>
       </c>
     </row>
-    <row r="311">
+    <row r="311" ht="60" customHeight="1">
       <c r="A311" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-opposition-sun-friend-gentle_specific</t>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="T311" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Lời bạn nói có thể chạm vào một mặt bạn ấy ít khi nhắc tới; chọn lúc riêng tư và hỏi bạn ấy có muốn nghe không. (Đoán nội tâm: “một mặt bạn ấy chưa muốn nhìn” khẳng định bạn ấy đang né tránh.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu lời bạn định nói liên quan chuyện bạn ấy ít nhắc tới, chọn lúc riêng tư và hỏi họ có muốn nghe không. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -30933,7 +30933,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="60" customHeight="1">
       <c r="A316" s="4" t="inlineStr">
         <is>
           <t>R03-mercury-opposition-sun-partner-playful_grounded</t>
@@ -31025,7 +31025,7 @@
       </c>
       <c r="T316" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Người yêu bảo năm nay sẽ tiết kiệm, bạn kể ngay ba đơn hàng tháng trước: trí nhớ kiểm toán viên, sắc mà hơi lạnh. (“mở lịch sử chuyển khoản ra đối chiếu” bình thường hóa việc soi giao dịch của người yêu, lệch giá trị riêng tư/tôn trọng của app.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Người yêu vừa kể kế hoạch tiết kiệm, bạn đã nhớ ba lần cả hai đặt đồ: xin phép góp ý trước khi mở phiên kiểm toán. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -32853,7 +32853,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="60" customHeight="1">
       <c r="A336" s="4" t="inlineStr">
         <is>
           <t>R03-moon-opposition-sun-someone-playful_grounded</t>
@@ -32945,7 +32945,7 @@
       </c>
       <c r="T336" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Người này là sân khấu, bạn là phòng chờ: không cần đổi chỗ, chỉ cần biết lúc nào mình nên về nghỉ. (“lúc nào nên tắt đèn” mơ hồ, không rõ hành động và có thể gợi nghĩa thân mật với người mới quen.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Buổi gặp đông người, bạn đã cạn pin mà vẫn ngồi nghe hết chuyện: hôm nay được phép về trước phần hỏi đáp. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -34389,7 +34389,7 @@
         </is>
       </c>
     </row>
-    <row r="352">
+    <row r="352" ht="60" customHeight="1">
       <c r="A352" s="4" t="inlineStr">
         <is>
           <t>R03-moon-sextile-mercury-someone-playful_grounded</t>
@@ -34481,7 +34481,7 @@
       </c>
       <c r="T352" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn buột miệng kể hôm nay mệt, người này kể lại chuyện mệt của họ: chưa thân lắm mà đã có chung chủ đề than thở. (Lặp khung: “hội … có N thành viên” (5 lần).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn vừa than mệt, người này cũng kể ngày dài của họ: chưa thân lắm, đã chung một chủ đề để nghỉ giải lao. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -34773,7 +34773,7 @@
         </is>
       </c>
     </row>
-    <row r="356">
+    <row r="356" ht="60" customHeight="1">
       <c r="A356" s="4" t="inlineStr">
         <is>
           <t>R03-moon-square-moon-crush-playful_grounded</t>
@@ -34865,7 +34865,7 @@
       </c>
       <c r="T356" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn buồn thì muốn tâm sự, crush buồn có khi lại lặn mất: hai hệ điều hành cảm xúc, cần cài thêm bộ chuyển đổi. (Đoán ý người kia như sự thật: “crush buồn thì muốn biến mất”; thêm rào “có khi” và đổi sang hành vi.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn buồn thì nhắn dài, crush có khi im một lúc: khung chat chưa kèm phụ đề, hỏi trước khi tự dịch nhé. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -38997,7 +38997,7 @@
         </is>
       </c>
     </row>
-    <row r="400">
+    <row r="400" ht="60" customHeight="1">
       <c r="A400" s="4" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-venus-someone-playful_grounded</t>
@@ -39089,7 +39089,7 @@
       </c>
       <c r="T400" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn nói chuyện như thường ngày, người này cười nhiều hơn dự kiến: đôi khi bớt chuẩn bị lại là chuẩn bị tốt nhất. (Lặp khung: punchline gần trùng dòng crush cùng contact (“chế độ bình thường của bạn đã đủ thú vị” / “phiên bản mặc định khá được”).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn thôi tập câu mở đầu mà người này lại cười nhiều hơn: hôm nay bản không diễn tập cũng có đất dùng. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -45141,7 +45141,7 @@
         </is>
       </c>
     </row>
-    <row r="464">
+    <row r="464" ht="60" customHeight="1">
       <c r="A464" s="4" t="inlineStr">
         <is>
           <t>R03-venus-trine-mercury-someone-playful_grounded</t>
@@ -45233,7 +45233,7 @@
       </c>
       <c r="T464" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn hỏi thêm một câu về điều người này vừa nói, họ hào hứng giải thích cả buổi: câu hỏi đúng chỗ mở được nhiều cửa. (Lặp kịch bản: gần trùng jupiter-trine-sun-someone-playful (khen ý → họ nói thêm nhiều ý); khung “hệ thống …” lặp.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn hỏi thêm một câu, người này kể cả buổi: phần hỏi đáp dài hơn dự kiến, nhớ chừa lượt cho mình. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -45717,7 +45717,7 @@
         </is>
       </c>
     </row>
-    <row r="470">
+    <row r="470" ht="60" customHeight="1">
       <c r="A470" s="4" t="inlineStr">
         <is>
           <t>R03-moon-trine-moon-friend-straight_warm</t>
@@ -45809,7 +45809,7 @@
       </c>
       <c r="T470" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn và bạn ấy dễ cần những thứ giống nhau khi mệt và chăm nhau theo cùng một kiểu; những buổi ngồi không bên nhau cũng quý. (Không tự nhiên: “cùng kiểu cần” thiếu tân ngữ.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu bạn và bạn ấy hay chọn cùng cách nghỉ khi mệt, những buổi ngồi yên bên nhau cũng đáng giữ; vẫn hỏi xem ai cần gì. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -47637,7 +47637,7 @@
         </is>
       </c>
     </row>
-    <row r="490">
+    <row r="490" ht="60" customHeight="1">
       <c r="A490" s="4" t="inlineStr">
         <is>
           <t>R03-venus-square-mars-partner-straight_warm</t>
@@ -47729,7 +47729,7 @@
       </c>
       <c r="T490" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Khi bạn muốn một tối nhẹ nhàng bên nhau mà người yêu đang hừng hực muốn ra ngoài, hai nhịp dễ lệch; nói rõ bạn đang cần gì. (“muốn gần gũi nhẹ nhàng” + “hừng hực năng lượng” (Kim–Hỏa, partner) dễ đọc thành ẩn ý tình dục; làm rõ cảnh đời thường.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Khi bạn muốn tối yên bên nhau mà người yêu rủ ra ngoài, hai người có thể lệch ý; nói rõ bạn cần gì hôm nay. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -48213,7 +48213,7 @@
         </is>
       </c>
     </row>
-    <row r="496">
+    <row r="496" ht="60" customHeight="1">
       <c r="A496" s="4" t="inlineStr">
         <is>
           <t>R03-venus-square-mars-someone-playful_grounded</t>
@@ -48305,7 +48305,7 @@
       </c>
       <c r="T496" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn cười chào xã giao, người này đã gửi kết bạn trên ba mạng: hai bên đang chạy hai tốc độ khác nhau. (Bản cũ nói người kia hiểu bạn thế nào (đoán ý)). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn cười chào xã giao, người này gửi kết bạn ba mạng: khoan bật đủ thông báo, bạn được chọn nhịp của mình. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -50133,7 +50133,7 @@
         </is>
       </c>
     </row>
-    <row r="516">
+    <row r="516" ht="60" customHeight="1">
       <c r="A516" s="4" t="inlineStr">
         <is>
           <t>R03-neptune-trine-venus-crush-playful_grounded</t>
@@ -50225,7 +50225,7 @@
       </c>
       <c r="T516" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Bạn gửi một playlist mộng mơ, crush gửi lại một playlist khác: cuộc trò chuyện bằng nhạc vừa mở màn, nghe tiếp xem sao. (Lặp khung: “hội … có N thành viên” xuất hiện 5 lần; bản sửa thêm lời mời quan sát.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Bạn gửi playlist mộng mơ, crush gửi lại một playlist khác: cuộc chat bằng nhạc đã mở, đừng tự thêm lời tỏ tình. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -51957,7 +51957,7 @@
         </is>
       </c>
     </row>
-    <row r="535">
+    <row r="535" ht="48" customHeight="1">
       <c r="A535" s="4" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-true_node-friend-gentle_specific</t>
@@ -52049,11 +52049,11 @@
       </c>
       <c r="T535" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể bạn ấy hay để ý cách bạn tự tin xử lý mọi việc; ở bên và khích lệ khi bạn ấy thử là đủ. (Đoán nội tâm, hơi bề trên: “sự tự tin của bạn là điều bạn ấy đang tập” khẳng định điểm yếu của bạn ấy.). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="536">
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Lúc bạn ấy hỏi cách bạn làm rồi thử theo, chia sẻ phần hữu ích và để bạn ấy tự chọn cách riêng. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="48" customHeight="1">
       <c r="A536" s="4" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-true_node-friend-playful_grounded</t>
@@ -52145,7 +52145,7 @@
       </c>
       <c r="T536" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Thấy bạn đọc sách, bạn ấy cũng ôm về một chồng: thói quen tốt mà lây được thì cứ để nó lây. (Lặp khung: “… không lương / miễn phí / không thu phí” xuất hiện 5 lần.). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Thấy bạn đọc sách, bạn ấy cũng ôm về một chồng: hội đọc chưa họp, danh sách mượn đã dài. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -53877,7 +53877,7 @@
         </is>
       </c>
     </row>
-    <row r="555">
+    <row r="555" ht="60" customHeight="1">
       <c r="A555" s="4" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-uranus-partner-gentle_specific</t>
@@ -53969,7 +53969,7 @@
       </c>
       <c r="T555" s="6" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: viết lại → Có thể những lần người yêu muốn đổi mới nếp sống lại chạm vào chỗ bạn cần ổn định; nói rõ điều gì cần giữ nguyên. (Gán nhu cầu (“nhu cầu tự do của người yêu”) và tối nghĩa (“được nhìn nhận ổn định”).). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: viết lại → Nếu người yêu đề nghị đổi nếp sống lúc bạn cần ổn định, nói rõ điều bạn muốn giữ trước khi bàn phần thay đổi. | Codex chuốt 26/10; Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -54807,7 +54807,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="26.399999618530273" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-crush-deep_dive</t>
@@ -54835,11 +54835,11 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Cách crush sống sôi nổi đôi khi làm bạn chao đảo với hướng mới đang tập, nên ghi lại lý do mình bắt đầu rồi xem sau vài lần gặp nó còn vững không.</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>34</v>
+          <t xml:space="preserve">Nếu lời rủ của crush làm bạn lưỡng lự với nếp mới đang tập, ghi lại điều mình muốn giữ rồi nói rõ, vì bạn không cần đổi hướng chỉ để theo kịp người khác.</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <v>35</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -54942,7 +54942,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="26.399999618530273" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>R03-true_node-square-sun-someone-deep_dive</t>
@@ -54970,10 +54970,10 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Thứ hiện ra rõ nhất là giọng chắc nịch của người này đôi khi làm bạn lung lay; dùng lúc đó để hỏi lại hướng của mình, vì người khác không quyết thay bạn.</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="n">
+          <t xml:space="preserve">Nếu bạn đổi ý ngay sau khi nghe người này trình bày, dành lúc riêng xem lại lý do ban đầu, vì giọng nói tự tin chưa đủ để quyết thay điều bạn chọn.</t>
+        </is>
+      </c>
+      <c r="G9" s="9">
         <v>34</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
@@ -54983,7 +54983,7 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -55077,7 +55077,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="26.399999618530273" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>R03-jupiter-trine-pluto-partner-deep_dive</t>
@@ -55105,11 +55105,11 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Một mẫu hay lặp lại là người yêu nói ra nỗi lo sâu nhất vào những tối bạn giữ giọng bình tĩnh; ghi nhận trước khi động viên, rồi đối chiếu qua vài tuần.</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>34</v>
+          <t xml:space="preserve">Nếu người yêu kể chuyện lo lắng lúc bạn giữ giọng bình tĩnh, ghi nhận trước khi động viên rồi hỏi họ cần gì, vì một lần nói chuyện chưa cho biết cách nào luôn phù hợp.</t>
+        </is>
+      </c>
+      <c r="G12" s="9">
+        <v>37</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -55212,7 +55212,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="26.399999618530273" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>R03-jupiter-trine-sun-friend-deep_dive</t>
@@ -55240,11 +55240,11 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Bạn thường nhận vai người cổ vũ sớm nhất mỗi lần bạn ấy cân nhắc một bước ngoặt; hỏi xem kiểu cổ vũ nào giúp được bạn ấy thật, thay vì đoán.</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>32</v>
+          <t xml:space="preserve">Trước một bước ngoặt của bạn ấy, bạn có thể hỏi muốn được lắng nghe hay góp ý rồi mới cổ vũ, vì điều giúp ích là do bạn ấy nói, không phải mình đoán.</t>
+        </is>
+      </c>
+      <c r="G15" s="9">
+        <v>35</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
@@ -55253,7 +55253,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -55482,7 +55482,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="26.399999618530273" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
           <t>R03-mercury-square-sun-someone-deep_dive</t>
@@ -55510,11 +55510,11 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Giữa bạn và người này, câu hỏi vặn đôi khi bật ra ngay lúc họ kể điều mình làm được; mở bằng một lời ghi nhận, rồi để ý không khí buổi trao đổi thay đổi ra sao.</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>38</v>
+          <t xml:space="preserve">Nếu bạn hỏi dồn lúc người này vừa kể thành quả, ghi nhận một việc cụ thể trước khi hỏi thêm, rồi để ý họ đáp ra sao thay vì tự đoán ý sau vẻ mặt.</t>
+        </is>
+      </c>
+      <c r="G21" s="9">
+        <v>36</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
@@ -55523,7 +55523,7 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -55617,7 +55617,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="26.399999618530273" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
           <t>R03-mercury-trine-true_node-partner-deep_dive</t>
@@ -55645,11 +55645,11 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Trong những bữa tối, câu hỏi bạn đặt ra dễ giúp người yêu vạch rõ bước tiếp theo; để họ tự trả lời, rồi xem hướng đó có thành hình qua vài tháng.</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>33</v>
+          <t xml:space="preserve">Nếu câu hỏi của bạn giúp người yêu nói rõ việc tiếp theo, để họ tự chọn bước muốn làm và hỏi lại khi họ nhắc tới, vì nói được chưa có nghĩa là đã quyết.</t>
+        </is>
+      </c>
+      <c r="G24" s="9">
+        <v>36</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -55658,7 +55658,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -55977,7 +55977,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="26.399999618530273" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
           <t>R03-sun-trine-venus-partner-deep_dive</t>
@@ -56005,11 +56005,11 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>Nhìn qua nhiều ngày, những hôm bạn tự tin làm việc mình giỏi thường đi cùng cử chỉ chăm sóc của người yêu; gọi tên cử chỉ đó, nhưng không cần phải giỏi mới được chăm.</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>36</v>
+          <t xml:space="preserve">Nếu bạn nhận thấy người yêu quan tâm khi mình kể việc làm tốt, ghi nhận cử chỉ cụ thể ấy và nói điều bạn cần, vì bạn không cần giỏi mới xứng đáng được quan tâm.</t>
+        </is>
+      </c>
+      <c r="G32" s="9">
+        <v>37</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
@@ -56018,7 +56018,7 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -56202,7 +56202,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="26.399999618530273" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
           <t>R03-venus-square-jupiter-someone-deep_dive</t>
@@ -56230,11 +56230,11 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Điều cần đọc kỹ là những kế hoạch lớn người này đưa ra ngay lần đầu dễ làm bạn ngợp, nên nhìn vào những gì họ làm sau đó, và bạn được quyền đi chậm.</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>35</v>
+          <t xml:space="preserve">Nếu bạn thấy ngợp khi người này đề nghị những việc lớn ngay lần đầu, nói rõ phần mình sẵn sàng làm rồi quan sát cách họ đáp, vì bạn được quyền chọn mức tham gia.</t>
+        </is>
+      </c>
+      <c r="G37" s="9">
+        <v>36</v>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -56787,7 +56787,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="26.399999618530273" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
           <t>R03-venus-trine-mars-crush-deep_dive</t>
@@ -56815,10 +56815,10 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>Điều lớp này ghi nhận là sự ân cần nhỏ của bạn hay được crush trả lời bằng việc làm, như hẹn một buổi cụ thể; nhìn chuỗi hành động qua vài tuần thay vì một lời mời.</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="n">
+          <t xml:space="preserve">Nếu bạn quan tâm bằng lời còn crush đáp bằng một lời hẹn cụ thể, đối chiếu thêm những lần sau và giữ nhịp mình thấy thoải mái, vì một lời mời chưa xác định mối quan hệ.</t>
+        </is>
+      </c>
+      <c r="G50" s="9">
         <v>38</v>
       </c>
       <c r="H50" s="9" t="inlineStr">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -56922,7 +56922,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="26.399999618530273" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
           <t>R03-venus-trine-mars-someone-deep_dive</t>
@@ -56950,10 +56950,10 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Một quan sát đáng giữ là sự thân thiện của bạn dễ dẫn tới việc người này đề nghị làm chung một việc; bạn được quyền cân nhắc, vì một lời mời chưa nói lên mức thân.</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="n">
+          <t xml:space="preserve">Nếu lời bắt chuyện của bạn dẫn tới đề nghị làm chung việc gì đó, cứ hỏi rõ phần mình rồi cân nhắc, vì một lời mời chưa nói lên mức độ thân quen giữa hai người.</t>
+        </is>
+      </c>
+      <c r="G53" s="9">
         <v>37</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -56963,7 +56963,7 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -57012,7 +57012,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="26.399999618530273" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
           <t>R03-venus-trine-sun-friend-deep_dive</t>
@@ -57040,10 +57040,10 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Vai quen của bạn là người ghi nhận khi bạn ấy vượt qua một việc khó, như sau kỳ thi hay buổi ra mắt sản phẩm, nên giữ thói quen nhắn một câu, rồi xem cách bạn ấy đáp.</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="n">
+          <t xml:space="preserve">Khi bạn ấy kể vừa vượt qua một việc khó, lời ghi nhận cụ thể của bạn có thể mở thêm cuộc trò chuyện, nhưng vẫn hỏi họ có muốn kể tiếp thay vì tự nhận vai động viên.</t>
+        </is>
+      </c>
+      <c r="G55" s="9">
         <v>39</v>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -57053,11 +57053,11 @@
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26.399999618530273" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
           <t>R03-venus-trine-sun-partner-deep_dive</t>
@@ -57085,11 +57085,11 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>Lớp đầu tiên là một câu cảm ơn có tên việc cụ thể, như “cảm ơn vì đã sửa vòi nước”, thường làm người yêu hăng hái hơn với việc chung; thử một tuần rồi xem nhà mình đổi gì.</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="n">
-        <v>40</v>
+          <t xml:space="preserve">Một lời cảm ơn gọi tên việc cụ thể, như sửa vòi nước, có thể giúp hai bạn nói rõ sự quan tâm; hỏi người yêu việc nào có ý nghĩa, thay vì tự đánh giá hộ họ.</t>
+        </is>
+      </c>
+      <c r="G56" s="9">
+        <v>38</v>
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -57192,7 +57192,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="26.399999618530273" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
           <t>R03-mars-sextile-moon-friend-deep_dive</t>
@@ -57220,11 +57220,11 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>Ở các kèo nhóm, bạn đứng ra lên lịch còn bạn ấy tới với tâm trạng thoải mái, một nhịp khá dễ đi; hỏi ý trước khi chốt, rồi xem bạn ấy có rủ lại không.</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="n">
-        <v>36</v>
+          <t xml:space="preserve">Khi lên lịch gặp nhóm, bạn có thể hỏi phần nào giúp bạn ấy thoải mái rồi mới chốt; để ý cả những lần họ chủ động rủ lại, vì phối hợp cần lượt của hai người.</t>
+        </is>
+      </c>
+      <c r="G59" s="9">
+        <v>37</v>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -57552,7 +57552,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="26.399999618530273" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
           <t>R03-mars-trine-sun-friend-deep_dive</t>
@@ -57580,11 +57580,11 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Nhìn qua những thử thách hai đứa từng làm, bạn hay là người rủ còn bạn ấy là người tỏa sáng khi làm, nên để bạn ấy tự nhận phần việc và hỏi lại khi thấy nhịp quá dày.</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="n">
-        <v>39</v>
+          <t xml:space="preserve">Nếu bạn khởi xướng một việc còn bạn ấy nhận phần làm sở trường, chia rõ phạm vi và hỏi lịch có vừa không, vì làm tốt một lần chưa nói lên cách phối hợp lâu dài.</t>
+        </is>
+      </c>
+      <c r="G67" s="9">
+        <v>37</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
@@ -57593,11 +57593,11 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26.399999618530273" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
           <t>R03-mars-trine-sun-partner-deep_dive</t>
@@ -57625,11 +57625,11 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>Nhìn theo tuần, kế hoạch bạn khởi xướng như tập thể dục hay nấu món mới thường là chỗ người yêu thể hiện sở trường; luân phiên người khởi xướng, rồi sau một tháng hỏi nhau nhịp có vừa không.</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="n">
-        <v>40</v>
+          <t xml:space="preserve">Khi bạn rủ tập hay nấu món mới, để người yêu chọn phần họ muốn thử rồi luân phiên khởi xướng; hỏi lại sau vài lần, vì một người luôn lên lịch cũng có thể thấy mệt.</t>
+        </is>
+      </c>
+      <c r="G68" s="9">
+        <v>37</v>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -57957,7 +57957,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="26.399999618530273" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
           <t>R03-mercury-conjunction-venus-partner-deep_dive</t>
@@ -57985,11 +57985,11 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Theo nếp hằng ngày, những tin nhắn nhỏ kiểu “về cẩn thận nhé” của bạn thường được người yêu nhắc lại vào hôm sau, nên để ý xem chúng có thưa đi vào tuần bận không, rồi tự điều chỉnh.</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="n">
-        <v>40</v>
+          <t xml:space="preserve">Với những tin nhắn hỏi han hằng ngày, bạn có thể để ý lúc nào người yêu đáp lại và hỏi họ cách nào dễ chịu, vì tuần bận ít tin chưa nói lên mức độ quan tâm.</t>
+        </is>
+      </c>
+      <c r="G76" s="9">
+        <v>38</v>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -58092,7 +58092,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="26.399999618530273" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
           <t>R03-mercury-opposition-sun-friend-deep_dive</t>
@@ -58120,11 +58120,11 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Trong nhiều buổi cà phê, góc nhìn của bạn về một chuyện thường ngược với cách bạn ấy kể, nên xin phép trước khi phản biện, và để ý không khí giữa hai đứa sau mỗi lần bàn.</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="n">
-        <v>38</v>
+          <t xml:space="preserve">Nếu cách bạn hiểu một chuyện khác với lời bạn ấy kể, xin phép trước khi góp ý rồi nghe câu trả lời, vì góc nhìn khác không tự động là hiểu rõ người kia hơn.</t>
+        </is>
+      </c>
+      <c r="G79" s="9">
+        <v>36</v>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
@@ -58133,7 +58133,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -58182,7 +58182,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="26.399999618530273" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>R03-mercury-opposition-sun-someone-deep_dive</t>
@@ -58210,10 +58210,10 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Ghi nhận đầu tiên là ý kiến của bạn và người này hay đứng ở hai đầu, kể cả trong chuyện nhỏ; để họ nói xong rồi mới đáp, vì khác góc nhìn không phải chuyện đúng sai.</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="n">
+          <t xml:space="preserve">Nếu bạn và người này nêu hai ý trái nhau, để họ nói hết rồi hỏi lại phần mình chưa rõ trước khi đáp, vì một bất đồng chưa mô tả được cả cách hai người hợp tác.</t>
+        </is>
+      </c>
+      <c r="G81" s="9">
         <v>38</v>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -58223,7 +58223,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -58272,7 +58272,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="26.399999618530273" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>R03-moon-opposition-sun-friend-deep_dive</t>
@@ -58300,11 +58300,11 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Những tuần bạn ấy bận chạy dự án hay trùng lúc bạn mong một buổi ngồi gần nói chuyện; giữ một lịch cố định mỗi tháng rồi xem hai đứa có đỡ hụt nhau không.</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="n">
-        <v>35</v>
+          <t xml:space="preserve">Nếu lịch bận của bạn ấy trùng lúc bạn muốn gặp, đề xuất một dịp cụ thể rồi hỏi thời gian nào vừa, vì chưa sắp được một buổi không có nghĩa là tình bạn kém quan trọng.</t>
+        </is>
+      </c>
+      <c r="G83" s="9">
+        <v>38</v>
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
@@ -58313,11 +58313,11 @@
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26.399999618530273" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
           <t>R03-moon-opposition-sun-partner-deep_dive</t>
@@ -58345,11 +58345,11 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Một mẫu dễ thấy là những mùa người yêu bận rộn bên ngoài, buổi tối của bạn ở nhà dài ra; đề xuất một tối cố định trong tuần, rồi xem một tháng sau có giữ được không.</t>
-        </is>
-      </c>
-      <c r="G84" s="9" t="n">
-        <v>38</v>
+          <t xml:space="preserve">Nếu người yêu bận bên ngoài lúc bạn mong có buổi tối chung, nói rõ điều mình cần rồi cùng chọn thời gian, vì lịch bận và mong muốn gần nhau cần được hỏi riêng từng người.</t>
+        </is>
+      </c>
+      <c r="G84" s="9">
+        <v>37</v>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
@@ -58358,7 +58358,7 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -58452,7 +58452,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="26.399999618530273" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>R03-moon-sextile-mercury-friend-deep_dive</t>
@@ -58480,11 +58480,11 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Hay gặp ở hai bạn là một tin than thở ngắn của bạn được bạn ấy đáp bằng lời khá trúng; nhắn trước cũng được, miễn là nhìn xem bạn ấy có đang bận hay không.</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="n">
-        <v>36</v>
+          <t xml:space="preserve">Nếu một tin than thở của bạn được bạn ấy đáp đúng điều đang cần, ghi nhận câu ấy rồi hỏi lúc nào tiện kể tiếp, vì sự lắng nghe cũng cần thời gian của cả hai.</t>
+        </is>
+      </c>
+      <c r="G87" s="9">
+        <v>37</v>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -58947,7 +58947,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="26.399999618530273" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-venus-crush-deep_dive</t>
@@ -58975,10 +58975,10 @@
       </c>
       <c r="F98" s="9" t="inlineStr">
         <is>
-          <t>Điều hiện ra là những hôm bạn để lộ nét riêng của mình, crush thường đáp bằng câu hỏi và lời hẹn gặp lại; ghi lại qua vài tuần, vì vài lần trùng hợp chưa thành nếp.</t>
-        </is>
-      </c>
-      <c r="G98" s="9" t="n">
+          <t xml:space="preserve">Khi bạn kể chuyện bằng giọng tự nhiên, để ý cách crush tiếp lời qua nhiều lần và hỏi nếu chưa rõ, vì một câu hỏi thêm chưa có nghĩa là người ấy muốn tiến xa hơn.</t>
+        </is>
+      </c>
+      <c r="G98" s="9">
         <v>37</v>
       </c>
       <c r="H98" s="9" t="inlineStr">
@@ -58988,11 +58988,11 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring; cần chuốt: câu dễ cấn hơi nghiêng về mô tả người kia hoặc ngầm hứa tiến triển</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="26.399999618530273" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-venus-friend-deep_dive</t>
@@ -59020,10 +59020,10 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>Nhìn qua những lần gặp, bạn ấy hay nhớ những chi tiết nhỏ bạn từng kể và nhắc lại đúng lúc; ghi nhận điều đó, rồi xem bạn có làm điều tương tự cho bạn ấy không.</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="n">
+          <t xml:space="preserve">Nếu bạn ấy nhớ và nhắc lại chi tiết nhỏ bạn từng kể, ghi nhận việc ấy rồi xem mình có lắng nghe tương tự không, vì một tình bạn cần chỗ kể cho cả hai người.</t>
+        </is>
+      </c>
+      <c r="G99" s="9">
         <v>37</v>
       </c>
       <c r="H99" s="9" t="inlineStr">
@@ -59033,7 +59033,7 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -59127,7 +59127,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="26.399999618530273" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
           <t>R03-sun-square-mercury-crush-deep_dive</t>
@@ -59155,10 +59155,10 @@
       </c>
       <c r="F102" s="9" t="inlineStr">
         <is>
-          <t>Chỗ dễ cấn là ngay sau khi bạn khoe một thành quả, crush hay hỏi lại từng chi tiết nhỏ; trả lời trước rồi mới quyết có buồn không, và nhìn cả cuộc chat thay vì một câu.</t>
-        </is>
-      </c>
-      <c r="G102" s="9" t="n">
+          <t xml:space="preserve">Nếu crush hỏi kỹ ngay sau khi bạn khoe thành quả, bạn có thể thấy hụt; nói rõ hôm nay mình muốn chia vui hay xin ý kiến, rồi xem họ đáp, thay vì đoán từ một câu.</t>
+        </is>
+      </c>
+      <c r="G102" s="9">
         <v>38</v>
       </c>
       <c r="H102" s="9" t="inlineStr">
@@ -59168,7 +59168,7 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -59307,7 +59307,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="26.399999618530273" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
           <t>R03-sun-trine-moon-crush-deep_dive</t>
@@ -59335,11 +59335,11 @@
       </c>
       <c r="F106" s="9" t="inlineStr">
         <is>
-          <t>Một quan sát nhẹ là crush thường kể chuyện chậm rãi và dài hơn khi bạn giữ giọng bình thản; xem họ có tự tìm đến bạn để kể không, vì đó mới là tín hiệu rõ.</t>
-        </is>
-      </c>
-      <c r="G106" s="9" t="n">
-        <v>37</v>
+          <t xml:space="preserve">Nếu crush kể dài hơn lúc bạn nói chuyện bình thản, cứ lắng nghe và hỏi họ có muốn kể tiếp, vì một cuộc trò chuyện dễ chịu chưa xác định tình cảm của người kia.</t>
+        </is>
+      </c>
+      <c r="G106" s="9">
+        <v>36</v>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
@@ -59348,11 +59348,11 @@
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="26.399999618530273" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
           <t>R03-sun-trine-moon-friend-deep_dive</t>
@@ -59380,11 +59380,11 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>Nhìn lại những lần gần đây, bạn thường là chỗ bạn ấy ghé qua sau một ngày rối, và buổi gặp hay kết thúc nhẹ nhõm; vai này quý, nhưng cũng cần có ngày bạn được nghe lại.</t>
-        </is>
-      </c>
-      <c r="G107" s="9" t="n">
-        <v>38</v>
+          <t xml:space="preserve">Nếu bạn ấy hay tìm tới bạn sau ngày khó, hỏi lúc này muốn được nghe hay góp ý, và nói rõ khi bạn cần nghỉ, vì quan tâm không đồng nghĩa với luôn có mặt.</t>
+        </is>
+      </c>
+      <c r="G107" s="9">
+        <v>36</v>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
@@ -59393,7 +59393,7 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -59487,7 +59487,7 @@
         </is>
       </c>
     </row>
-    <row r="110">
+    <row r="110" ht="26.399999618530273" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
           <t>R03-sun-trine-sun-crush-deep_dive</t>
@@ -59515,11 +59515,11 @@
       </c>
       <c r="F110" s="9" t="inlineStr">
         <is>
-          <t>Xét theo những buổi đi chơi, năng lượng của bạn và crush thường lên xuống khá cùng nhịp; thử vài kiểu hoạt động khác nhau, và đừng coi một buổi vui là câu trả lời.</t>
-        </is>
-      </c>
-      <c r="G110" s="9" t="n">
-        <v>35</v>
+          <t xml:space="preserve">Nếu bạn và crush hào hứng với cùng hoạt động, thử một dịp phù hợp cả hai rồi hỏi buổi đó thế nào, vì một lần vui chưa trả lời được toàn bộ chuyện giữa hai người.</t>
+        </is>
+      </c>
+      <c r="G110" s="9">
+        <v>37</v>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
@@ -59528,7 +59528,7 @@
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
@@ -60567,7 +60567,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="26.399999618530273" customHeight="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-true_node-crush-deep_dive</t>
@@ -60595,11 +60595,11 @@
       </c>
       <c r="F134" s="9" t="inlineStr">
         <is>
-          <t>Một điều lớp này ghi lại là vài nếp sống của bạn đôi khi được crush thử theo; vui với điều đó, và nhớ họ đi hướng nào vẫn là lựa chọn của họ.</t>
-        </is>
-      </c>
-      <c r="G134" s="9" t="n">
-        <v>34</v>
+          <t xml:space="preserve">Nếu crush hỏi rồi thử một nếp sống bạn chia sẻ, cứ nói phần hữu ích và để họ làm theo cách riêng, vì việc thử ấy chưa nói lên tình cảm hay hướng họ sẽ chọn.</t>
+        </is>
+      </c>
+      <c r="G134" s="9">
+        <v>37</v>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
@@ -60608,11 +60608,11 @@
       </c>
       <c r="I134" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="26.399999618530273" customHeight="1">
       <c r="A135" s="9" t="inlineStr">
         <is>
           <t>R03-sun-conjunction-true_node-friend-deep_dive</t>
@@ -60640,11 +60640,11 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>Theo những lần gặp, bạn ấy hay mượn vài cách làm của bạn rồi biến tấu theo kiểu riêng; khen phần biến tấu đó, và để bạn ấy tự quyết đi tiếp tới đâu.</t>
-        </is>
-      </c>
-      <c r="G135" s="9" t="n">
-        <v>34</v>
+          <t xml:space="preserve">Nếu bạn ấy thử cách làm của bạn rồi biến tấu, hỏi phần nào phù hợp và ghi nhận lựa chọn riêng ấy, vì chia sẻ kinh nghiệm không có nghĩa là quyết giúp họ bước tiếp theo.</t>
+        </is>
+      </c>
+      <c r="G135" s="9">
+        <v>38</v>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
-          <t>Uỷ quyền 26/10: duyệt bản nháp (giọng deep_dive cho phép tối đa 40 âm tiết). Codex chuốt trước khi wiring</t>
+          <t xml:space="preserve">Uỷ quyền 26/10: duyệt bản nháp; Codex chuốt 26/10 để giữ tình huống có điều kiện, không giả định lịch sử gặp hay ý người kia. Claude review trước khi wiring.</t>
         </is>
       </c>
     </row>
